--- a/artfynd/A 260-2023 artfynd.xlsx
+++ b/artfynd/A 260-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126557809</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>126557074</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 260-2023 artfynd.xlsx
+++ b/artfynd/A 260-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126557809</v>
       </c>
       <c r="B2" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>126557074</v>
       </c>
       <c r="B3" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 260-2023 artfynd.xlsx
+++ b/artfynd/A 260-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126557809</v>
       </c>
       <c r="B2" t="n">
-        <v>98359</v>
+        <v>98353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>126557074</v>
       </c>
       <c r="B3" t="n">
-        <v>98359</v>
+        <v>98353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 260-2023 artfynd.xlsx
+++ b/artfynd/A 260-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126557809</v>
+        <v>126557073</v>
       </c>
       <c r="B2" t="n">
-        <v>98359</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382171</v>
+        <v>382213</v>
       </c>
       <c r="R2" t="n">
-        <v>6637123</v>
+        <v>6637102</v>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I bankslänt på en 40m sträcka</t>
+          <t>I dikesbotten och ytterslänt på norra sidan vägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,12 +787,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rasmus Mild</t>
+          <t>Otto Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rasmus Mild</t>
+          <t>Otto Nilsson, Rasmus Mild</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -806,7 +806,7 @@
         <v>126557074</v>
       </c>
       <c r="B3" t="n">
-        <v>98359</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,6 +924,514 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126557075</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Finnängen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>381893</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6637265</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gräsmark</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I inner- och ytterslänt på norra sidan vägen. Längs en sträcka på ca 20m</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Otto Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Otto Nilsson, Rasmus Mild</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126557809</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dammyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>382171</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6637123</v>
+      </c>
+      <c r="S5" t="n">
+        <v>22</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gräsmark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I bankslänt på en 40m sträcka</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rasmus Mild</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rasmus Mild</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126557810</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Finnängen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>381892</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6637256</v>
+      </c>
+      <c r="S6" t="n">
+        <v>22</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gräsmark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På en 10 m sträcka i bankslänt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rasmus Mild</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rasmus Mild</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126557088</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dammyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>382243</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6637090</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gräsmark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I innerslänt och ytterslänt på norra sidan vägen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Otto Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Otto Nilsson, Rasmus Mild</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
